--- a/artfynd/A 39974-2025 artfynd.xlsx
+++ b/artfynd/A 39974-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937328</v>
+        <v>119937324</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542433</v>
+        <v>542547</v>
       </c>
       <c r="R2" t="n">
-        <v>7012114</v>
+        <v>7011995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>119937325</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937324</v>
+        <v>119937328</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542547</v>
+        <v>542433</v>
       </c>
       <c r="R4" t="n">
-        <v>7011995</v>
+        <v>7012114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937326</v>
+        <v>119937327</v>
       </c>
       <c r="B5" t="n">
-        <v>79659</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937327</v>
+        <v>119937326</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 39974-2025 artfynd.xlsx
+++ b/artfynd/A 39974-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937325</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937327</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>